--- a/templates/modelo-carga-vendas.xlsx
+++ b/templates/modelo-carga-vendas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Carga Vendas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carga Vendas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,11 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
-    <numFmt numFmtId="166" formatCode="R$ #,##0.00"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="165" formatCode="R$ #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -68,17 +67,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -501,7 +503,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>%MB</t>
+          <t>MC1%</t>
         </is>
       </c>
     </row>
@@ -516,7 +518,7 @@
           <t>Máquinas</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="8" t="n">
         <v>46176</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -537,10 +539,10 @@
       <c r="G2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H2" s="9" t="n">
         <v>184500</v>
       </c>
-      <c r="I2" s="6" t="n">
+      <c r="I2" s="10" t="n">
         <v>0.318</v>
       </c>
     </row>
@@ -555,7 +557,7 @@
           <t>Máquinas</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="8" t="n">
         <v>46184</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -576,10 +578,10 @@
       <c r="G3" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="9" t="n">
         <v>92000</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I3" s="10" t="n">
         <v>0.242</v>
       </c>
     </row>
@@ -594,7 +596,7 @@
           <t>Máquinas</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="8" t="n">
         <v>46197</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -615,10 +617,10 @@
       <c r="G4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="9" t="n">
         <v>92250</v>
       </c>
-      <c r="I4" s="6" t="n"/>
+      <c r="I4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -631,7 +633,7 @@
           <t>Máquinas</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="8" t="n">
         <v>46218</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -652,10 +654,10 @@
       <c r="G5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="9" t="n">
         <v>215000</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="10" t="n">
         <v>0.295</v>
       </c>
     </row>
@@ -670,7 +672,7 @@
           <t>Transgrain</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="8" t="n">
         <v>46191</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -691,10 +693,10 @@
       <c r="G6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="9" t="n">
         <v>45000</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="10" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -709,7 +711,7 @@
           <t>Acessórios</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="8" t="n">
         <v>46200</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -726,10 +728,10 @@
       <c r="G7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="9" t="n">
         <v>8900</v>
       </c>
-      <c r="I7" s="6" t="n"/>
+      <c r="I7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -742,7 +744,7 @@
           <t>Peças</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="8" t="n">
         <v>46193</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -757,10 +759,10 @@
       </c>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="9" t="n">
         <v>12500</v>
       </c>
-      <c r="I8" s="6" t="n"/>
+      <c r="I8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -773,18 +775,19 @@
           <t>Peças</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="8" t="n">
         <v>46208</v>
       </c>
       <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="n"/>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="9" t="n">
         <v>4300</v>
       </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
+      <c r="I9" s="10" t="n"/>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
@@ -851,10 +854,11 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>%MB         -&gt; margem bruta em % (OPCIONAL; ex: 31,8% = 0,318).</t>
-        </is>
-      </c>
-    </row>
+          <t>MC1%         -&gt; MC1 em % (OPCIONAL; ex: 31,8% = 0,318).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
